--- a/artfynd/A 12033-2026 artfynd.xlsx
+++ b/artfynd/A 12033-2026 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>98943121</v>
+        <v>98943070</v>
       </c>
       <c r="B2" t="n">
-        <v>56315</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57899</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102110</v>
+        <v>100067</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Buteo lagopus</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,7 +708,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
@@ -727,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>666242.0098105092</v>
+        <v>666242</v>
       </c>
       <c r="R2" t="n">
-        <v>6545536.60697132</v>
+        <v>6545537</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -777,7 +776,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Cirklade över norra delen av Muskan och drog troligen iväg åt sydost.</t>
+          <t>Cirklade över norra delen av Muskan och drog förmodligen iväg åt sydost.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,49 +791,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Göran Holmberg</t>
+          <t>Göran E Holmberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Göran Holmberg</t>
+          <t>Göran E Holmberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>98943070</v>
+        <v>98943121</v>
       </c>
       <c r="B3" t="n">
-        <v>56311</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57903</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100067</v>
+        <v>102110</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Fjällvråk</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Buteo lagopus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -842,11 +836,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
@@ -860,10 +850,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>666242.0098105092</v>
+        <v>666242</v>
       </c>
       <c r="R3" t="n">
-        <v>6545536.60697132</v>
+        <v>6545537</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -910,7 +900,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Cirklade över norra delen av Muskan och drog förmodligen iväg åt sydost.</t>
+          <t>Cirklade över norra delen av Muskan och drog troligen iväg åt sydost.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,12 +915,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Göran Holmberg</t>
+          <t>Göran E Holmberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Göran Holmberg</t>
+          <t>Göran E Holmberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 12033-2026 artfynd.xlsx
+++ b/artfynd/A 12033-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -800,6 +805,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98943070</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -924,8 +934,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98943121</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>